--- a/Kachi_Gun/Table/Mine.xlsx
+++ b/Kachi_Gun/Table/Mine.xlsx
@@ -824,7 +824,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Max_Gems_Ad_x3 (광고3배)</t>
+          <t>Max_Gems_Ad_x2 (광고2배)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -856,25 +856,25 @@
         <v>0</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>1</v>
+        <v>1.428</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>11.2</v>
+        <v>28.8</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>33.6</v>
+        <v>57.7</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>67.2</v>
+        <v>115.4</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -892,28 +892,28 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1.15</v>
+        <v>1.428</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>12.8</v>
+        <v>28.8</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>38.4</v>
+        <v>57.7</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>76.8</v>
+        <v>115.4</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -931,28 +931,28 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.15</v>
+        <v>1.714</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1.3</v>
+        <v>3.142</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.3</v>
+        <v>3.14</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>14.6</v>
+        <v>63.5</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>43.8</v>
+        <v>126.9</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>87.59999999999999</v>
+        <v>253.9</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -970,28 +970,28 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.15</v>
+        <v>1.428</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1.45</v>
+        <v>4.57</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.45</v>
+        <v>4.57</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>16.1</v>
+        <v>92.3</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>48.3</v>
+        <v>184.6</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>96.59999999999999</v>
+        <v>369.3</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -1009,28 +1009,28 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.15</v>
+        <v>1.429</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1.6</v>
+        <v>5.999</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>17.9</v>
+        <v>121.2</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>53.7</v>
+        <v>242.4</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>107.4</v>
+        <v>484.7</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.15</v>
+        <v>1.713</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1.75</v>
+        <v>7.712</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.18</v>
+        <v>0.77</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1.75</v>
+        <v>7.71</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>19.7</v>
+        <v>155.8</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>59.1</v>
+        <v>311.6</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>118.2</v>
+        <v>623.1</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1087,28 +1087,28 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.15</v>
+        <v>1.429</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1.9</v>
+        <v>9.141</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.19</v>
+        <v>0.91</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1.9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>21.3</v>
+        <v>184.6</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>63.9</v>
+        <v>369.3</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>127.8</v>
+        <v>738.6</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1126,28 +1126,28 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.15</v>
+        <v>1.428</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2.05</v>
+        <v>10.569</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.2</v>
+        <v>1.06</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2.05</v>
+        <v>10.57</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>22.9</v>
+        <v>213.5</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>68.7</v>
+        <v>427</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>137.4</v>
+        <v>854</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1165,28 +1165,28 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.15</v>
+        <v>1.428</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2.2</v>
+        <v>11.997</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.22</v>
+        <v>1.2</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>24.6</v>
+        <v>242.3</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>73.8</v>
+        <v>484.7</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>147.6</v>
+        <v>969.4</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1204,28 +1204,28 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.15</v>
+        <v>1.714</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2.35</v>
+        <v>13.711</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.24</v>
+        <v>1.37</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>2.35</v>
+        <v>13.71</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>26.4</v>
+        <v>277</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>79.2</v>
+        <v>553.9</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>158.4</v>
+        <v>1107.8</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
@@ -1243,28 +1243,28 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.25</v>
+        <v>1.428</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2.6</v>
+        <v>15.139</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.26</v>
+        <v>1.51</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>2.6</v>
+        <v>15.14</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>29.1</v>
+        <v>305.8</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>87.3</v>
+        <v>611.6</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>174.6</v>
+        <v>1223.2</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1282,28 +1282,28 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2.85</v>
+        <v>17.139</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.29</v>
+        <v>1.71</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2.85</v>
+        <v>17.14</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>32</v>
+        <v>346.2</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>96</v>
+        <v>692.4</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>192</v>
+        <v>1384.8</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1321,28 +1321,28 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.25</v>
+        <v>2.57</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3.1</v>
+        <v>19.709</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.31</v>
+        <v>1.97</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3.1</v>
+        <v>19.71</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>34.7</v>
+        <v>398.1</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>104.1</v>
+        <v>796.2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>208.2</v>
+        <v>1592.5</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1360,28 +1360,28 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.25</v>
+        <v>2.143</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>3.35</v>
+        <v>21.852</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.34</v>
+        <v>2.19</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3.35</v>
+        <v>21.85</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>37.6</v>
+        <v>441.4</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>112.8</v>
+        <v>882.8</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>225.6</v>
+        <v>1765.6</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1399,28 +1399,28 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.25</v>
+        <v>2.142</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3.6</v>
+        <v>23.994</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>3.6</v>
+        <v>23.99</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>40.3</v>
+        <v>484.7</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>120.9</v>
+        <v>969.4</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>241.8</v>
+        <v>1938.7</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1438,28 +1438,28 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.25</v>
+        <v>2.571</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>3.85</v>
+        <v>26.565</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.39</v>
+        <v>2.66</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3.85</v>
+        <v>26.57</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>43.2</v>
+        <v>536.6</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>129.6</v>
+        <v>1073.2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>259.2</v>
+        <v>2146.5</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -1477,28 +1477,28 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.25</v>
+        <v>2.142</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>4.1</v>
+        <v>28.707</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.41</v>
+        <v>2.87</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4.1</v>
+        <v>28.71</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>45.9</v>
+        <v>579.9</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>137.7</v>
+        <v>1159.8</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>275.4</v>
+        <v>2319.5</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -1516,28 +1516,28 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.25</v>
+        <v>2.143</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4.35</v>
+        <v>30.85</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.43</v>
+        <v>3.09</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4.35</v>
+        <v>30.85</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>48.6</v>
+        <v>623.2</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>145.8</v>
+        <v>1246.3</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>291.6</v>
+        <v>2492.7</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.25</v>
+        <v>2.142</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4.6</v>
+        <v>32.992</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.46</v>
+        <v>3.3</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>4.6</v>
+        <v>32.99</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>51.5</v>
+        <v>666.4</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>154.5</v>
+        <v>1332.9</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>309</v>
+        <v>2665.8</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1594,28 +1594,28 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.25</v>
+        <v>2.571</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4.85</v>
+        <v>35.563</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.48</v>
+        <v>3.56</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4.85</v>
+        <v>35.56</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>54.2</v>
+        <v>718.4</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>162.6</v>
+        <v>1436.7</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>325.2</v>
+        <v>2873.5</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1633,28 +1633,28 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.4</v>
+        <v>2.428</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5.25</v>
+        <v>37.991</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.53</v>
+        <v>3.8</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>5.25</v>
+        <v>37.99</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>58.9</v>
+        <v>767.4</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>176.7</v>
+        <v>1534.8</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>353.4</v>
+        <v>3069.7</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1672,28 +1672,28 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.4</v>
+        <v>2.856</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5.65</v>
+        <v>40.847</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.57</v>
+        <v>4.08</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>5.65</v>
+        <v>40.85</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>63.4</v>
+        <v>825.1</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>190.2</v>
+        <v>1650.2</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>380.4</v>
+        <v>3300.4</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -1711,28 +1711,28 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.4</v>
+        <v>3.428</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>6.05</v>
+        <v>44.275</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.6</v>
+        <v>4.43</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>6.05</v>
+        <v>44.27</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>67.59999999999999</v>
+        <v>894.4</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>202.8</v>
+        <v>1788.7</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>405.6</v>
+        <v>3577.4</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -1750,28 +1750,28 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.4</v>
+        <v>2.856</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>6.45</v>
+        <v>47.131</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.65</v>
+        <v>4.71</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>6.45</v>
+        <v>47.13</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>72.40000000000001</v>
+        <v>952</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>217.2</v>
+        <v>1904.1</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>434.4</v>
+        <v>3808.2</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.4</v>
+        <v>2.857</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>6.85</v>
+        <v>49.988</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>5</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>6.85</v>
+        <v>49.99</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>76.8</v>
+        <v>1009.8</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>230.4</v>
+        <v>2019.5</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>460.8</v>
+        <v>4039</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -1828,28 +1828,28 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.4</v>
+        <v>2.856</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>7.25</v>
+        <v>52.844</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.73</v>
+        <v>5.28</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>7.25</v>
+        <v>52.84</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>81.3</v>
+        <v>1067.4</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>243.9</v>
+        <v>2134.9</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>487.8</v>
+        <v>4269.8</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -1867,28 +1867,28 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.4</v>
+        <v>3.428</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>7.65</v>
+        <v>56.272</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.77</v>
+        <v>5.63</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>7.65</v>
+        <v>56.27</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>85.8</v>
+        <v>1136.7</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>257.4</v>
+        <v>2273.4</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>514.8</v>
+        <v>4546.8</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -1906,28 +1906,28 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.4</v>
+        <v>2.856</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>59.128</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>8.050000000000001</v>
+        <v>59.13</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>90.3</v>
+        <v>1194.4</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>270.9</v>
+        <v>2388.8</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>541.8</v>
+        <v>4777.5</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -1945,28 +1945,28 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.4</v>
+        <v>2.857</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>61.985</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.84</v>
+        <v>6.2</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>8.449999999999999</v>
+        <v>61.98</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>94.5</v>
+        <v>1252.1</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>283.5</v>
+        <v>2504.2</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>567</v>
+        <v>5008.4</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -1984,28 +1984,28 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.4</v>
+        <v>3.427</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>8.85</v>
+        <v>65.41200000000001</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.89</v>
+        <v>6.54</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>8.85</v>
+        <v>65.41</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>99.2</v>
+        <v>1321.3</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>297.6</v>
+        <v>2642.6</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>595.2</v>
+        <v>5285.3</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/Kachi_Gun/Table/Mine.xlsx
+++ b/Kachi_Gun/Table/Mine.xlsx
@@ -856,22 +856,22 @@
         <v>0</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>1.428</v>
+        <v>1.089</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>28.8</v>
+        <v>22</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>57.7</v>
+        <v>44</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>115.4</v>
+        <v>88</v>
       </c>
       <c r="K2" s="9" t="n">
         <v>560</v>
@@ -895,22 +895,22 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1.428</v>
+        <v>1.089</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>28.8</v>
+        <v>22</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>57.7</v>
+        <v>44</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>115.4</v>
+        <v>88</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>560</v>
@@ -931,25 +931,25 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1.714</v>
+        <v>1.307</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3.142</v>
+        <v>2.396</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>63.5</v>
+        <v>48.4</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>126.9</v>
+        <v>96.8</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>253.9</v>
+        <v>193.6</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>560</v>
@@ -970,25 +970,25 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1.428</v>
+        <v>1.089</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>4.57</v>
+        <v>3.485</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.46</v>
+        <v>0.35</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>4.57</v>
+        <v>3.48</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>92.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>184.6</v>
+        <v>140.8</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>369.3</v>
+        <v>281.6</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>560</v>
@@ -1009,25 +1009,25 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1.429</v>
+        <v>1.089</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>5.999</v>
+        <v>4.574</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>6</v>
+        <v>4.57</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>121.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>242.4</v>
+        <v>184.8</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>484.7</v>
+        <v>369.6</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>560</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1.713</v>
+        <v>1.307</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>7.712</v>
+        <v>5.881</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>7.71</v>
+        <v>5.88</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>155.8</v>
+        <v>118.8</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>311.6</v>
+        <v>237.6</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>623.1</v>
+        <v>475.2</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>560</v>
@@ -1087,25 +1087,25 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1.429</v>
+        <v>1.089</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>9.141</v>
+        <v>6.97</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>9.140000000000001</v>
+        <v>6.97</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>184.6</v>
+        <v>140.8</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>369.3</v>
+        <v>281.6</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>738.6</v>
+        <v>563.2</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>560</v>
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1.428</v>
+        <v>1.089</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>10.569</v>
+        <v>8.058999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>10.57</v>
+        <v>8.06</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>213.5</v>
+        <v>162.8</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>427</v>
+        <v>325.6</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>854</v>
+        <v>651.2</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>560</v>
@@ -1165,25 +1165,25 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1.428</v>
+        <v>1.09</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>11.997</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1.2</v>
+        <v>0.91</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>12</v>
+        <v>9.15</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>242.3</v>
+        <v>184.8</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>484.7</v>
+        <v>369.6</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>969.4</v>
+        <v>739.2</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>560</v>
@@ -1204,25 +1204,25 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.714</v>
+        <v>1.306</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>13.711</v>
+        <v>10.455</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>13.71</v>
+        <v>10.46</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>277</v>
+        <v>211.2</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>553.9</v>
+        <v>422.4</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1107.8</v>
+        <v>844.8</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>560</v>
@@ -1243,25 +1243,25 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.428</v>
+        <v>1.09</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>15.139</v>
+        <v>11.545</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1.51</v>
+        <v>1.15</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>15.14</v>
+        <v>11.54</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>305.8</v>
+        <v>233.2</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>611.6</v>
+        <v>466.4</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1223.2</v>
+        <v>932.8</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>560</v>
@@ -1282,25 +1282,25 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>1.524</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>17.139</v>
+        <v>13.069</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>17.14</v>
+        <v>13.07</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>346.2</v>
+        <v>264</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>692.4</v>
+        <v>528</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1384.8</v>
+        <v>1056</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>560</v>
@@ -1321,25 +1321,25 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2.57</v>
+        <v>1.961</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>19.709</v>
+        <v>15.03</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>19.71</v>
+        <v>15.03</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>398.1</v>
+        <v>303.6</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>796.2</v>
+        <v>607.2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1592.5</v>
+        <v>1214.4</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>560</v>
@@ -1360,25 +1360,25 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2.143</v>
+        <v>1.633</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>21.852</v>
+        <v>16.663</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>21.85</v>
+        <v>16.66</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>441.4</v>
+        <v>336.6</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>882.8</v>
+        <v>673.2</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1765.6</v>
+        <v>1346.4</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>560</v>
@@ -1399,25 +1399,25 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2.142</v>
+        <v>1.634</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>23.994</v>
+        <v>18.297</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>23.99</v>
+        <v>18.3</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>484.7</v>
+        <v>369.6</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>969.4</v>
+        <v>739.2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1938.7</v>
+        <v>1478.4</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>560</v>
@@ -1438,25 +1438,25 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2.571</v>
+        <v>1.96</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>26.565</v>
+        <v>20.257</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2.66</v>
+        <v>2.03</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>26.57</v>
+        <v>20.26</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>536.6</v>
+        <v>409.2</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1073.2</v>
+        <v>818.4</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2146.5</v>
+        <v>1636.8</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>560</v>
@@ -1477,25 +1477,25 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>2.142</v>
+        <v>1.634</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>28.707</v>
+        <v>21.891</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>2.87</v>
+        <v>2.19</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>28.71</v>
+        <v>21.89</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>579.9</v>
+        <v>442.2</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>1159.8</v>
+        <v>884.4</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2319.5</v>
+        <v>1768.8</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>560</v>
@@ -1516,25 +1516,25 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2.143</v>
+        <v>1.634</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>30.85</v>
+        <v>23.525</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>3.09</v>
+        <v>2.35</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>30.85</v>
+        <v>23.52</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>623.2</v>
+        <v>475.2</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>1246.3</v>
+        <v>950.4</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2492.7</v>
+        <v>1900.8</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>560</v>
@@ -1555,25 +1555,25 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2.142</v>
+        <v>1.633</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>32.992</v>
+        <v>25.158</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>32.99</v>
+        <v>25.16</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>666.4</v>
+        <v>508.2</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>1332.9</v>
+        <v>1016.4</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2665.8</v>
+        <v>2032.8</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>560</v>
@@ -1594,25 +1594,25 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2.571</v>
+        <v>1.961</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>35.563</v>
+        <v>27.119</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>35.56</v>
+        <v>27.12</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>718.4</v>
+        <v>547.8</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1436.7</v>
+        <v>1095.6</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>2873.5</v>
+        <v>2191.2</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>560</v>
@@ -1633,25 +1633,25 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2.428</v>
+        <v>1.851</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>37.991</v>
+        <v>28.97</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>37.99</v>
+        <v>28.97</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>767.4</v>
+        <v>585.2</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1534.8</v>
+        <v>1170.4</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>3069.7</v>
+        <v>2340.8</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>560</v>
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2.856</v>
+        <v>2.179</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>40.847</v>
+        <v>31.149</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>4.08</v>
+        <v>3.11</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>40.85</v>
+        <v>31.15</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>825.1</v>
+        <v>629.2</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>1650.2</v>
+        <v>1258.4</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>3300.4</v>
+        <v>2516.8</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>560</v>
@@ -1711,25 +1711,25 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3.428</v>
+        <v>2.613</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>44.275</v>
+        <v>33.762</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>4.43</v>
+        <v>3.38</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>44.27</v>
+        <v>33.76</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>894.4</v>
+        <v>682</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>1788.7</v>
+        <v>1364</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>3577.4</v>
+        <v>2728</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>560</v>
@@ -1750,25 +1750,25 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>2.856</v>
+        <v>2.179</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>47.131</v>
+        <v>35.941</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>4.71</v>
+        <v>3.59</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>47.13</v>
+        <v>35.94</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>952</v>
+        <v>726</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1904.1</v>
+        <v>1452</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>3808.2</v>
+        <v>2904</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>560</v>
@@ -1789,25 +1789,25 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>2.857</v>
+        <v>2.178</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>49.988</v>
+        <v>38.119</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>5</v>
+        <v>3.81</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>49.99</v>
+        <v>38.12</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1009.8</v>
+        <v>770</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2019.5</v>
+        <v>1540</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4039</v>
+        <v>3080</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>560</v>
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2.856</v>
+        <v>2.178</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>52.844</v>
+        <v>40.297</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>5.28</v>
+        <v>4.03</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>52.84</v>
+        <v>40.3</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1067.4</v>
+        <v>814</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>2134.9</v>
+        <v>1628</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>4269.8</v>
+        <v>3256</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>560</v>
@@ -1867,25 +1867,25 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3.428</v>
+        <v>2.614</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>56.272</v>
+        <v>42.911</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>5.63</v>
+        <v>4.29</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>56.27</v>
+        <v>42.91</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>1136.7</v>
+        <v>866.8</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2273.4</v>
+        <v>1733.6</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>4546.8</v>
+        <v>3467.2</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>560</v>
@@ -1906,25 +1906,25 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.856</v>
+        <v>2.178</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>59.128</v>
+        <v>45.089</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>5.91</v>
+        <v>4.51</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>59.13</v>
+        <v>45.09</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>1194.4</v>
+        <v>910.8</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>2388.8</v>
+        <v>1821.6</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>4777.5</v>
+        <v>3643.2</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>560</v>
@@ -1945,25 +1945,25 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>2.857</v>
+        <v>2.178</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>61.985</v>
+        <v>47.267</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>6.2</v>
+        <v>4.73</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>61.98</v>
+        <v>47.27</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1252.1</v>
+        <v>954.8</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>2504.2</v>
+        <v>1909.6</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>5008.4</v>
+        <v>3819.2</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>560</v>
@@ -1984,25 +1984,25 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3.427</v>
+        <v>2.614</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>65.41200000000001</v>
+        <v>49.881</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>6.54</v>
+        <v>4.99</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>65.41</v>
+        <v>49.88</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1321.3</v>
+        <v>1007.6</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>2642.6</v>
+        <v>2015.2</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>5285.3</v>
+        <v>4030.4</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>560</v>
